--- a/data/trans_camb/PCS12_SP_R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,9</t>
+          <t>-3,17; 2,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -0,29</t>
+          <t>-4,69; -0,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,57</t>
+          <t>-5,41; -0,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,17</t>
+          <t>-2,33; 4,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,06</t>
+          <t>-3,62; 2,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,73</t>
+          <t>-3,74; 4,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,2</t>
+          <t>-1,98; 2,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,25</t>
+          <t>-3,63; 0,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,93</t>
+          <t>-3,71; 0,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 69,72</t>
+          <t>-56,38; 77,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,72; -0,13</t>
+          <t>-84,57; 7,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-99,04; 23,18</t>
+          <t>-99,18; -2,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 109,21</t>
+          <t>-35,56; 107,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,77; 53,19</t>
+          <t>-51,8; 53,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,18; 115,78</t>
+          <t>-59,6; 110,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 56,95</t>
+          <t>-35,4; 52,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 9,27</t>
+          <t>-62,56; 1,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,35; 27,38</t>
+          <t>-68,13; 22,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,83</t>
+          <t>-0,22; 4,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,11</t>
+          <t>-1,86; 2,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 10,07</t>
+          <t>1,89; 9,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,71</t>
+          <t>-5,89; 0,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,68</t>
+          <t>-5,67; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 0,91</t>
+          <t>-6,57; 1,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,99</t>
+          <t>-1,82; 2,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,1</t>
+          <t>-2,68; 1,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,36</t>
+          <t>-1,01; 4,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 151,18</t>
+          <t>-4,88; 154,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,33; 100,29</t>
+          <t>-36,2; 88,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,67; 300,06</t>
+          <t>33,93; 303,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,93; 10,23</t>
+          <t>-52,37; 11,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,57; 8,83</t>
+          <t>-52,43; 8,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 11,61</t>
+          <t>-61,11; 12,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 33,75</t>
+          <t>-24,56; 36,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 21,87</t>
+          <t>-37,06; 22,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 72,18</t>
+          <t>-13,1; 75,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,86</t>
+          <t>-0,75; 4,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,1</t>
+          <t>-2,49; 3,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,9</t>
+          <t>1,7; 8,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,07</t>
+          <t>-2,23; 4,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -0,02</t>
+          <t>-6,84; 0,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 4,6</t>
+          <t>-2,43; 4,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,53</t>
+          <t>-1,0; 4,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,71</t>
+          <t>-4,06; 0,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,26</t>
+          <t>-0,06; 5,55</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 90,98</t>
+          <t>-8,99; 91,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 56,37</t>
+          <t>-29,73; 53,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,96; 157,34</t>
+          <t>21,54; 157,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 42,78</t>
+          <t>-14,8; 42,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 0,8</t>
+          <t>-44,34; 1,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 38,13</t>
+          <t>-15,72; 34,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 48,83</t>
+          <t>-8,49; 45,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 7,79</t>
+          <t>-33,25; 7,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 57,08</t>
+          <t>-0,56; 59,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,89</t>
+          <t>-2,33; 5,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 7,55</t>
+          <t>-0,17; 7,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 64,92</t>
+          <t>6,78; 65,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 1,09</t>
+          <t>-9,46; 0,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -0,12</t>
+          <t>-9,99; -0,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 3,81</t>
+          <t>-5,85; 4,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,03</t>
+          <t>-4,5; 2,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,27</t>
+          <t>-3,8; 2,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 42,22</t>
+          <t>3,17; 43,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 67,32</t>
+          <t>-17,49; 65,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 83,1</t>
+          <t>-3,0; 83,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,93; 694,73</t>
+          <t>55,7; 788,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 4,84</t>
+          <t>-35,0; 3,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,95; -0,45</t>
+          <t>-36,96; -1,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 16,91</t>
+          <t>-21,35; 21,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 13,21</t>
+          <t>-23,06; 13,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 14,12</t>
+          <t>-19,81; 15,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,35; 241,09</t>
+          <t>16,03; 268,6</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 1,7</t>
+          <t>-11,18; 1,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 1,55</t>
+          <t>-10,38; 1,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 8,77</t>
+          <t>-2,67; 9,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,6; 16,96</t>
+          <t>3,99; 17,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 9,42</t>
+          <t>-3,77; 9,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 9,37</t>
+          <t>-1,69; 9,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 7,86</t>
+          <t>-1,26; 7,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 4,07</t>
+          <t>-5,15; 3,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 7,41</t>
+          <t>-0,86; 7,35</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 6,1</t>
+          <t>-35,01; 7,2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 6,48</t>
+          <t>-33,06; 6,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 35,21</t>
+          <t>-8,49; 37,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,26; 57,03</t>
+          <t>10,55; 59,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 31,38</t>
+          <t>-10,41; 30,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 31,43</t>
+          <t>-4,54; 31,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 27,72</t>
+          <t>-3,43; 27,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 13,93</t>
+          <t>-15,54; 13,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 25,87</t>
+          <t>-2,45; 25,92</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 13,27</t>
+          <t>-2,92; 12,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 3,2</t>
+          <t>-11,69; 2,95</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,55; -0,04</t>
+          <t>-13,09; 0,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 7,39</t>
+          <t>-6,74; 7,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -1,94</t>
+          <t>-15,9; -1,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-48,72; -11,52</t>
+          <t>-50,01; -11,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 7,44</t>
+          <t>-4,09; 7,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,99; -2,2</t>
+          <t>-12,14; -1,25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -8,78</t>
+          <t>-35,55; -8,69</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 38,99</t>
+          <t>-7,11; 37,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 9,59</t>
+          <t>-28,23; 8,42</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 0,42</t>
+          <t>-30,52; 1,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 12,86</t>
+          <t>-10,42; 12,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-25,78; -3,41</t>
+          <t>-24,83; -2,17</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-76,82; -19,28</t>
+          <t>-78,83; -18,46</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 15,57</t>
+          <t>-7,58; 15,02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-24,77; -4,59</t>
+          <t>-23,01; -2,54</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-64,58; -17,69</t>
+          <t>-67,63; -17,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 11,78</t>
+          <t>-6,63; 11,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 3,55</t>
+          <t>-13,31; 3,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -1,35</t>
+          <t>-16,85; -0,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 8,57</t>
+          <t>-3,32; 8,5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 0,75</t>
+          <t>-13,03; 1,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 2,99</t>
+          <t>-7,53; 2,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 7,86</t>
+          <t>-1,96; 7,8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,41; -0,87</t>
+          <t>-10,75; -0,59</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,68; -0,48</t>
+          <t>-9,77; -0,44</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 18,91</t>
+          <t>-9,34; 18,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 5,84</t>
+          <t>-18,76; 5,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,42; -2,43</t>
+          <t>-23,82; -1,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 11,25</t>
+          <t>-3,81; 11,1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 1,01</t>
+          <t>-15,22; 1,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 3,94</t>
+          <t>-8,93; 3,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 10,83</t>
+          <t>-2,53; 10,78</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -1,24</t>
+          <t>-13,88; -0,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -0,71</t>
+          <t>-12,42; -0,59</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,92</t>
+          <t>0,19; 3,99</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,72</t>
+          <t>-0,84; 2,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5,13; 30,73</t>
+          <t>5,02; 26,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,1</t>
+          <t>-0,08; 4,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,98</t>
+          <t>-3,02; 1,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,88</t>
+          <t>-4,18; 3,76</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,45</t>
+          <t>0,63; 3,53</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,44</t>
+          <t>-1,45; 1,36</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2,55; 13,98</t>
+          <t>2,64; 15,35</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1,82; 26,22</t>
+          <t>1,08; 26,39</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 18,29</t>
+          <t>-5,02; 18,39</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>31,91; 197,18</t>
+          <t>30,71; 169,54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 15,83</t>
+          <t>-0,39; 16,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 3,73</t>
+          <t>-10,76; 4,6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 14,6</t>
+          <t>-14,66; 14,15</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,52; 16,51</t>
+          <t>2,79; 16,73</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 6,87</t>
+          <t>-6,57; 6,37</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11,77; 66,1</t>
+          <t>12,12; 71,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R3-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,08</t>
+          <t>-2,77</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-0,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,05</t>
+          <t>-3,03; 2,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -0,09</t>
+          <t>-4,61; -0,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; -0,48</t>
+          <t>-5,04; -0,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,24</t>
+          <t>-2,03; 4,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 2,12</t>
+          <t>-3,72; 2,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,77</t>
+          <t>-2,22; 6,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,13</t>
+          <t>-1,81; 2,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,01</t>
+          <t>-3,42; 0,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,89</t>
+          <t>-2,95; 1,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-72,47%</t>
+          <t>-65,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-35,81%</t>
+          <t>-15,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,38; 77,13</t>
+          <t>-57,25; 60,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,57; 7,81</t>
+          <t>-84,25; -2,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-99,18; -2,43</t>
+          <t>-94,1; 19,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,56; 107,25</t>
+          <t>-31,56; 106,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 53,11</t>
+          <t>-54,07; 59,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 110,36</t>
+          <t>-38,43; 156,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 52,33</t>
+          <t>-31,75; 54,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 1,5</t>
+          <t>-59,25; 7,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,13; 22,58</t>
+          <t>-54,8; 48,54</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-2,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,93</t>
+          <t>-0,24; 4,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,9</t>
+          <t>-1,88; 2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,92</t>
+          <t>2,16; 9,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,86</t>
+          <t>-5,84; 0,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 0,61</t>
+          <t>-5,54; 1,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,09</t>
+          <t>-5,14; 1,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,05</t>
+          <t>-1,86; 2,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,29</t>
+          <t>-2,67; 1,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,29</t>
+          <t>-0,41; 4,81</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129,79%</t>
+          <t>130,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-27,16%</t>
+          <t>-21,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 154,69</t>
+          <t>-8,99; 139,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 88,42</t>
+          <t>-36,57; 92,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,93; 303,32</t>
+          <t>41,01; 289,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,37; 11,36</t>
+          <t>-50,66; 12,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,43; 8,2</t>
+          <t>-50,37; 14,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 12,58</t>
+          <t>-46,97; 20,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 36,82</t>
+          <t>-25,35; 38,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 22,91</t>
+          <t>-36,78; 20,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 75,9</t>
+          <t>-6,58; 83,01</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>2,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,99</t>
+          <t>-0,86; 5,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,12</t>
+          <t>-2,34; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,71</t>
+          <t>0,63; 7,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,95</t>
+          <t>-3,08; 4,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,08</t>
+          <t>-6,98; 0,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,23</t>
+          <t>-2,71; 4,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,22</t>
+          <t>-0,83; 3,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,58</t>
+          <t>-3,93; 0,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,55</t>
+          <t>0,04; 5,05</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 91,71</t>
+          <t>-11,29; 98,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 53,36</t>
+          <t>-29,55; 60,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,54; 157,66</t>
+          <t>7,26; 131,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 42,43</t>
+          <t>-18,8; 35,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 1,25</t>
+          <t>-44,58; 0,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 34,81</t>
+          <t>-17,13; 40,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 45,32</t>
+          <t>-7,35; 43,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 7,41</t>
+          <t>-34,11; 10,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 59,89</t>
+          <t>0,37; 54,94</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30,48</t>
+          <t>8,49</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,0</t>
+          <t>4,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,91</t>
+          <t>-2,57; 6,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 7,95</t>
+          <t>-0,29; 7,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,78; 65,26</t>
+          <t>3,95; 12,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 0,85</t>
+          <t>-9,16; 0,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -0,23</t>
+          <t>-9,92; -0,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 4,36</t>
+          <t>-4,48; 4,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,11</t>
+          <t>-4,59; 1,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,44</t>
+          <t>-3,92; 2,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 43,67</t>
+          <t>1,05; 7,37</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>271,08%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-2,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 65,16</t>
+          <t>-19,42; 67,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 83,47</t>
+          <t>-3,33; 82,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55,7; 788,98</t>
+          <t>29,11; 140,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 3,77</t>
+          <t>-34,52; 3,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,96; -1,15</t>
+          <t>-37,19; -2,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 21,0</t>
+          <t>-16,28; 21,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 13,39</t>
+          <t>-23,9; 12,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 15,49</t>
+          <t>-20,29; 15,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,03; 268,6</t>
+          <t>4,62; 45,43</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>4,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>2,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 1,69</t>
+          <t>-11,44; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 1,7</t>
+          <t>-10,67; 1,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 9,34</t>
+          <t>-3,73; 7,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,99; 17,63</t>
+          <t>3,78; 16,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 9,05</t>
+          <t>-3,5; 9,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 9,48</t>
+          <t>-1,14; 10,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 7,66</t>
+          <t>-1,92; 7,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,89</t>
+          <t>-5,32; 3,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 7,35</t>
+          <t>-0,88; 7,06</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 7,2</t>
+          <t>-34,56; 4,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 6,53</t>
+          <t>-33,75; 5,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 37,2</t>
+          <t>-12,1; 29,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,55; 59,74</t>
+          <t>10,25; 57,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 30,77</t>
+          <t>-9,21; 31,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 31,73</t>
+          <t>-3,78; 33,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 27,1</t>
+          <t>-5,81; 25,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 13,63</t>
+          <t>-15,99; 11,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 25,92</t>
+          <t>-2,64; 24,66</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-6,22</t>
+          <t>-6,81</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-29,41</t>
+          <t>-13,22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-18,76</t>
+          <t>-10,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 12,95</t>
+          <t>-4,27; 12,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 2,95</t>
+          <t>-11,84; 2,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 0,6</t>
+          <t>-13,57; -0,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 7,55</t>
+          <t>-7,75; 7,26</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,9; -1,25</t>
+          <t>-16,03; -1,68</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-50,01; -11,04</t>
+          <t>-19,38; -7,15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 7,27</t>
+          <t>-3,39; 7,7</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -1,25</t>
+          <t>-12,19; -1,86</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-35,55; -8,69</t>
+          <t>-15,08; -5,62</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-16,3%</t>
+          <t>-17,84%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-48,13%</t>
+          <t>-21,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-37,11%</t>
+          <t>-20,93%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 37,51</t>
+          <t>-9,6; 37,25</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 8,42</t>
+          <t>-28,53; 9,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 1,74</t>
+          <t>-31,53; -0,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 12,7</t>
+          <t>-11,76; 12,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -2,17</t>
+          <t>-25,2; -2,74</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,83; -18,46</t>
+          <t>-29,52; -12,55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 15,02</t>
+          <t>-6,54; 15,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,01; -2,54</t>
+          <t>-22,94; -3,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-67,63; -17,78</t>
+          <t>-28,44; -12,01</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-9,63</t>
+          <t>-9,77</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-2,66</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-5,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 11,53</t>
+          <t>-5,76; 11,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 3,44</t>
+          <t>-14,13; 2,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -0,89</t>
+          <t>-16,98; -1,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 8,5</t>
+          <t>-3,56; 8,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 1,0</t>
+          <t>-12,0; 1,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 2,84</t>
+          <t>-7,84; 2,62</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 7,8</t>
+          <t>-2,3; 7,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -0,59</t>
+          <t>-10,91; -0,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,77; -0,44</t>
+          <t>-10,07; -0,86</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-14,38%</t>
+          <t>-14,59%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-2,9%</t>
+          <t>-3,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-7,27%</t>
+          <t>-7,63%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 18,46</t>
+          <t>-8,25; 19,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 5,52</t>
+          <t>-19,71; 4,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,82; -1,42</t>
+          <t>-23,88; -3,17</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 11,1</t>
+          <t>-4,12; 11,5</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 1,35</t>
+          <t>-14,64; 1,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 3,69</t>
+          <t>-9,24; 3,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 10,78</t>
+          <t>-2,93; 10,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -0,84</t>
+          <t>-14,08; -0,26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -0,59</t>
+          <t>-12,87; -1,48</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>4,29</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,99</t>
+          <t>0,1; 3,93</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,78</t>
+          <t>-0,95; 2,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5,02; 26,48</t>
+          <t>3,49; 7,09</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,28</t>
+          <t>-0,31; 4,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,18</t>
+          <t>-3,24; 1,29</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,76</t>
+          <t>1,06; 5,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,53</t>
+          <t>0,59; 3,48</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,36</t>
+          <t>-1,48; 1,41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2,64; 15,35</t>
+          <t>2,9; 5,59</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1,08; 26,39</t>
+          <t>0,95; 26,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 18,39</t>
+          <t>-5,64; 17,92</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>30,71; 169,54</t>
+          <t>20,55; 47,54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 16,33</t>
+          <t>-1,08; 15,62</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 4,6</t>
+          <t>-11,51; 4,87</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 14,15</t>
+          <t>3,69; 19,6</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,79; 16,73</t>
+          <t>2,54; 16,61</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 6,37</t>
+          <t>-6,71; 6,8</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>12,12; 71,05</t>
+          <t>12,94; 26,66</t>
         </is>
       </c>
     </row>
